--- a/reference.xlsx
+++ b/reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f3df39ef44ce0b8/Desktop/Jayanagar/notice dashboard/deepseek/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9E90BB0-F645-4AC5-9BEB-E3EB11C7FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{C9E90BB0-F645-4AC5-9BEB-E3EB11C7FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D814608-0CBB-4CCB-883B-8DDACD462F84}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{401F68F1-F04B-4EC2-AAB9-AA76FA2DF911}"/>
   </bookViews>
@@ -69,18 +69,9 @@
     <t>Bangalore Rural</t>
   </si>
   <si>
-    <t xml:space="preserve">Padmanabhanagar </t>
-  </si>
-  <si>
     <t xml:space="preserve">Anekal </t>
   </si>
   <si>
-    <t xml:space="preserve">C.V. Raman Nagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Govindraj Nagar </t>
-  </si>
-  <si>
     <t xml:space="preserve">Vijayanagar </t>
   </si>
   <si>
@@ -144,13 +135,22 @@
     <t xml:space="preserve">Hebbal </t>
   </si>
   <si>
-    <t xml:space="preserve">Chamrajpet </t>
-  </si>
-  <si>
     <t xml:space="preserve">Pulakeshinagar </t>
   </si>
   <si>
     <t xml:space="preserve">Chickpet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padmanabanagar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GovindrajaNagar </t>
+  </si>
+  <si>
+    <t>Chamrajpet</t>
+  </si>
+  <si>
+    <t>C.V. RamannNagar</t>
   </si>
 </sst>
 </file>
@@ -531,7 +531,7 @@
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -545,7 +545,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -657,7 +657,7 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -727,7 +727,7 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -755,7 +755,7 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -867,7 +867,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
@@ -881,7 +881,7 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>

--- a/reference.xlsx
+++ b/reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f3df39ef44ce0b8/Desktop/Jayanagar/notice dashboard/deepseek/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{C9E90BB0-F645-4AC5-9BEB-E3EB11C7FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D814608-0CBB-4CCB-883B-8DDACD462F84}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{C9E90BB0-F645-4AC5-9BEB-E3EB11C7FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE0D4070-1A93-4DEC-A1CC-CFBBEFD9C209}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{401F68F1-F04B-4EC2-AAB9-AA76FA2DF911}"/>
   </bookViews>
@@ -147,10 +147,10 @@
     <t xml:space="preserve">GovindrajaNagar </t>
   </si>
   <si>
-    <t>Chamrajpet</t>
-  </si>
-  <si>
     <t>C.V. RamannNagar</t>
+  </si>
+  <si>
+    <t>Chamrajapet</t>
   </si>
 </sst>
 </file>
@@ -685,7 +685,7 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>

--- a/reference.xlsx
+++ b/reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f3df39ef44ce0b8/Desktop/Jayanagar/notice dashboard/deepseek/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{C9E90BB0-F645-4AC5-9BEB-E3EB11C7FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE0D4070-1A93-4DEC-A1CC-CFBBEFD9C209}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{C9E90BB0-F645-4AC5-9BEB-E3EB11C7FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34441AF0-F8A9-4836-BFE4-5F9B5384733C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{401F68F1-F04B-4EC2-AAB9-AA76FA2DF911}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="40">
   <si>
     <t>Asmbly name</t>
   </si>
@@ -69,88 +69,85 @@
     <t>Bangalore Rural</t>
   </si>
   <si>
-    <t xml:space="preserve">Anekal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vijayanagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bangalore South </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sarvagnanagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basavanagudi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shivajinagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.T.M. Layout </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shanti Nagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayanagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gandhi Nagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahadevapura </t>
-  </si>
-  <si>
     <t xml:space="preserve">Yelahanka </t>
   </si>
   <si>
-    <t xml:space="preserve">K.R. Puram </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byatarayanapura </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yeshwanthpura </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rajarajeshwarinagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dasarahalli </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahalakshmi Layout </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malleshwaram </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rajajinagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bommanahalli </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hebbal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulakeshinagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chickpet </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padmanabanagar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">GovindrajaNagar </t>
-  </si>
-  <si>
     <t>C.V. RamannNagar</t>
   </si>
   <si>
     <t>Chamrajapet</t>
+  </si>
+  <si>
+    <t>K.R. Pura</t>
+  </si>
+  <si>
+    <t>Mahalakshmi Layout</t>
+  </si>
+  <si>
+    <t>Malleshwaram</t>
+  </si>
+  <si>
+    <t>Hebbal</t>
+  </si>
+  <si>
+    <t>Pulakeshinagar</t>
+  </si>
+  <si>
+    <t>Sarvagnanagar</t>
+  </si>
+  <si>
+    <t>Rajarajeshwarinagar</t>
+  </si>
+  <si>
+    <t>Shivajinagar</t>
+  </si>
+  <si>
+    <t>Shantinagar</t>
+  </si>
+  <si>
+    <t>Gandhinagar</t>
+  </si>
+  <si>
+    <t>Rajajinagar</t>
+  </si>
+  <si>
+    <t>Chickpet</t>
+  </si>
+  <si>
+    <t>Govindarajanagar</t>
+  </si>
+  <si>
+    <t>Vijayanagar</t>
+  </si>
+  <si>
+    <t>Basavanagudi</t>
+  </si>
+  <si>
+    <t>Padmanabanagar</t>
+  </si>
+  <si>
+    <t>B.T.M Layout</t>
+  </si>
+  <si>
+    <t>Jayanagar</t>
+  </si>
+  <si>
+    <t>Bommanahalli</t>
+  </si>
+  <si>
+    <t>Anekal</t>
+  </si>
+  <si>
+    <t>Byatarayanapura</t>
+  </si>
+  <si>
+    <t>Yeshwanthapura</t>
+  </si>
+  <si>
+    <t>Dasarahalli</t>
+  </si>
+  <si>
+    <t>Mahadevapura</t>
   </si>
 </sst>
 </file>
@@ -181,7 +178,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -189,14 +186,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,10 +530,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{913251AF-4225-4BBA-B065-72A97B2C6BB4}">
-  <dimension ref="B1:E29"/>
+  <dimension ref="B1:H29"/>
   <sheetFormatPr defaultColWidth="24.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="8.88671875"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -528,10 +550,11 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -543,9 +566,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
-        <v>25</v>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -557,9 +580,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>26</v>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>36</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -571,9 +594,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>27</v>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -585,9 +608,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>28</v>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -599,9 +622,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>29</v>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -613,9 +636,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>30</v>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -627,9 +650,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>31</v>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -641,9 +664,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>34</v>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -655,9 +678,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>35</v>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -669,9 +692,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
-        <v>16</v>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -683,9 +706,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>39</v>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -697,9 +720,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>18</v>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -711,9 +734,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>20</v>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -725,9 +748,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>22</v>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>25</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -740,8 +763,8 @@
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>32</v>
+      <c r="B17" t="s">
+        <v>26</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -754,8 +777,8 @@
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
-        <v>38</v>
+      <c r="B18" t="s">
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -768,8 +791,8 @@
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
-        <v>14</v>
+      <c r="B19" t="s">
+        <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -782,8 +805,8 @@
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>40</v>
+      <c r="B20" t="s">
+        <v>15</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
@@ -796,8 +819,8 @@
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
-        <v>36</v>
+      <c r="B21" t="s">
+        <v>27</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -810,8 +833,8 @@
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
-        <v>17</v>
+      <c r="B22" t="s">
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -824,8 +847,8 @@
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
-        <v>37</v>
+      <c r="B23" t="s">
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -838,8 +861,8 @@
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
-        <v>19</v>
+      <c r="B24" t="s">
+        <v>32</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -852,8 +875,8 @@
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
-        <v>21</v>
+      <c r="B25" t="s">
+        <v>33</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -866,8 +889,8 @@
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
-        <v>23</v>
+      <c r="B26" t="s">
+        <v>39</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
@@ -880,8 +903,8 @@
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
-        <v>33</v>
+      <c r="B27" t="s">
+        <v>34</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -894,8 +917,8 @@
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
-        <v>15</v>
+      <c r="B28" t="s">
+        <v>10</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -908,8 +931,8 @@
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
-        <v>13</v>
+      <c r="B29" t="s">
+        <v>35</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
